--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755095296_h_5.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755095296_h_5.xlsx
@@ -658,7 +658,7 @@
         <v>0.008428503609948769</v>
       </c>
       <c r="C2" t="n">
-        <v>31564890</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>31564890</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>23178686</v>
+        <v>4316034</v>
       </c>
       <c r="L2" t="n">
-        <v>13859203</v>
+        <v>2367465</v>
       </c>
       <c r="M2" t="n">
-        <v>3539553</v>
+        <v>542449</v>
       </c>
       <c r="N2" t="n">
-        <v>191787</v>
+        <v>16742</v>
       </c>
       <c r="O2" t="n">
-        <v>2083148</v>
+        <v>330086</v>
       </c>
       <c r="P2" t="n">
-        <v>811439</v>
+        <v>126522</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.999959409236908</v>
+        <v>0.9999977946281433</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9214245676994324</v>
+        <v>0.8543757796287537</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8309654593467712</v>
+        <v>0.7035667896270752</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7924957275390625</v>
+        <v>0.6262637376785278</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5251244306564331</v>
+        <v>0.1852134615182877</v>
       </c>
       <c r="V2" t="n">
-        <v>0.830784797668457</v>
+        <v>0.6805924773216248</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8925582766532898</v>
+        <v>0.7986390590667725</v>
       </c>
       <c r="X2" t="n">
-        <v>31564890</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>31564890</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>24075557</v>
+        <v>4803769</v>
       </c>
       <c r="AG2" t="n">
-        <v>14852679</v>
+        <v>2978917</v>
       </c>
       <c r="AH2" t="n">
-        <v>3997548</v>
+        <v>800192</v>
       </c>
       <c r="AI2" t="n">
-        <v>294942</v>
+        <v>59026</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2295467</v>
+        <v>459413</v>
       </c>
       <c r="AK2" t="n">
-        <v>900185</v>
+        <v>180092</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9565606117248535</v>
+        <v>0.9563109874725342</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112661480903625</v>
+        <v>0.9112939834594727</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580878376960754</v>
+        <v>0.8580310344696045</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6623296141624451</v>
+        <v>0.6617932319641113</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020044803619385</v>
+        <v>0.9019097685813904</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314298033714294</v>
+        <v>0.931449294090271</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002021233558325551</v>
       </c>
       <c r="C3" t="n">
-        <v>759</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>23178686</v>
+        <v>4316034</v>
       </c>
       <c r="E3" t="n">
-        <v>1934870</v>
+        <v>688508</v>
       </c>
       <c r="F3" t="n">
-        <v>24048</v>
+        <v>11406</v>
       </c>
       <c r="G3" t="n">
-        <v>2877</v>
+        <v>963</v>
       </c>
       <c r="H3" t="n">
-        <v>1255</v>
+        <v>649</v>
       </c>
       <c r="I3" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="J3" t="n">
-        <v>50081828</v>
+        <v>10016608</v>
       </c>
       <c r="K3" t="n">
-        <v>54528873</v>
+        <v>10576380</v>
       </c>
       <c r="L3" t="n">
-        <v>62507593</v>
+        <v>12058691</v>
       </c>
       <c r="M3" t="n">
-        <v>76059920</v>
+        <v>15072463</v>
       </c>
       <c r="N3" t="n">
-        <v>81028918</v>
+        <v>16166691</v>
       </c>
       <c r="O3" t="n">
-        <v>78677836</v>
+        <v>15665136</v>
       </c>
       <c r="P3" t="n">
-        <v>80583738</v>
+        <v>16104307</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9218912124633789</v>
+        <v>0.8601835966110229</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8491547107696533</v>
+        <v>0.7232374548912048</v>
       </c>
       <c r="T3" t="n">
-        <v>0.759349524974823</v>
+        <v>0.5811420083045959</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4303563237190247</v>
+        <v>0.1875686198472977</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8182473182678223</v>
+        <v>0.6477965116500854</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8394905924797058</v>
+        <v>0.6542222499847412</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>24075557</v>
+        <v>4803769</v>
       </c>
       <c r="Z3" t="n">
-        <v>989932</v>
+        <v>198330</v>
       </c>
       <c r="AA3" t="n">
-        <v>42706</v>
+        <v>8575</v>
       </c>
       <c r="AB3" t="n">
-        <v>33970</v>
+        <v>6824</v>
       </c>
       <c r="AC3" t="n">
-        <v>225</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>50083110</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>55412140</v>
+        <v>11092567</v>
       </c>
       <c r="AG3" t="n">
-        <v>63880556</v>
+        <v>12766203</v>
       </c>
       <c r="AH3" t="n">
-        <v>76325582</v>
+        <v>15263782</v>
       </c>
       <c r="AI3" t="n">
-        <v>81051985</v>
+        <v>16210177</v>
       </c>
       <c r="AJ3" t="n">
-        <v>78852750</v>
+        <v>15770083</v>
       </c>
       <c r="AK3" t="n">
-        <v>80615145</v>
+        <v>16122953</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575626254081726</v>
+        <v>0.9573889374732971</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100250601768494</v>
+        <v>0.9100300669670105</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8576043844223022</v>
+        <v>0.8572698831558228</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6618287563323975</v>
+        <v>0.6612964868545532</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016448855400085</v>
+        <v>0.9016017913818359</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313045144081116</v>
+        <v>0.9312229752540588</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03189864197131144</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1867500</v>
+        <v>696877</v>
       </c>
       <c r="E4" t="n">
-        <v>13859203</v>
+        <v>2367465</v>
       </c>
       <c r="F4" t="n">
-        <v>544213</v>
+        <v>185327</v>
       </c>
       <c r="G4" t="n">
-        <v>15995</v>
+        <v>7496</v>
       </c>
       <c r="H4" t="n">
-        <v>32050</v>
+        <v>15133</v>
       </c>
       <c r="I4" t="n">
-        <v>2209</v>
+        <v>1129</v>
       </c>
       <c r="J4" t="n">
-        <v>1282</v>
+        <v>14</v>
       </c>
       <c r="K4" t="n">
-        <v>1976587</v>
+        <v>735647</v>
       </c>
       <c r="L4" t="n">
-        <v>2819231</v>
+        <v>997482</v>
       </c>
       <c r="M4" t="n">
-        <v>926784</v>
+        <v>323718</v>
       </c>
       <c r="N4" t="n">
-        <v>173435</v>
+        <v>73651</v>
       </c>
       <c r="O4" t="n">
-        <v>424298</v>
+        <v>154912</v>
       </c>
       <c r="P4" t="n">
-        <v>97677</v>
+        <v>31900</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999796748161316</v>
+        <v>0.9999988675117493</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9216578006744385</v>
+        <v>0.8572698831558228</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8399616479873657</v>
+        <v>0.7132664918899536</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7755686044692993</v>
+        <v>0.6028597354888916</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4730406701564789</v>
+        <v>0.1863835901021957</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8244684338569641</v>
+        <v>0.663789689540863</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8652114868164062</v>
+        <v>0.7192530632019043</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1020717</v>
+        <v>204872</v>
       </c>
       <c r="Z4" t="n">
-        <v>14852679</v>
+        <v>2978917</v>
       </c>
       <c r="AA4" t="n">
-        <v>414267</v>
+        <v>82914</v>
       </c>
       <c r="AB4" t="n">
-        <v>27445</v>
+        <v>5508</v>
       </c>
       <c r="AC4" t="n">
-        <v>5728</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>340</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1093320</v>
+        <v>219460</v>
       </c>
       <c r="AG4" t="n">
-        <v>1446268</v>
+        <v>289970</v>
       </c>
       <c r="AH4" t="n">
-        <v>661122</v>
+        <v>132399</v>
       </c>
       <c r="AI4" t="n">
-        <v>150368</v>
+        <v>30165</v>
       </c>
       <c r="AJ4" t="n">
-        <v>249384</v>
+        <v>49965</v>
       </c>
       <c r="AK4" t="n">
-        <v>66270</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9570613503456116</v>
+        <v>0.9568496942520142</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106451869010925</v>
+        <v>0.9106615781784058</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578459620475769</v>
+        <v>0.8576502799987793</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6620790362358093</v>
+        <v>0.6615447402000427</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018246531486511</v>
+        <v>0.901755690574646</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313670992851257</v>
+        <v>0.9313361048698425</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>349</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>66702</v>
+        <v>24895</v>
       </c>
       <c r="E5" t="n">
-        <v>766035</v>
+        <v>265985</v>
       </c>
       <c r="F5" t="n">
-        <v>3539553</v>
+        <v>542449</v>
       </c>
       <c r="G5" t="n">
-        <v>66121</v>
+        <v>25346</v>
       </c>
       <c r="H5" t="n">
-        <v>209456</v>
+        <v>68756</v>
       </c>
       <c r="I5" t="n">
-        <v>13080</v>
+        <v>5988</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1963854</v>
+        <v>701539</v>
       </c>
       <c r="L5" t="n">
-        <v>2461973</v>
+        <v>905962</v>
       </c>
       <c r="M5" t="n">
-        <v>1121743</v>
+        <v>390970</v>
       </c>
       <c r="N5" t="n">
-        <v>253860</v>
+        <v>72516</v>
       </c>
       <c r="O5" t="n">
-        <v>462718</v>
+        <v>179466</v>
       </c>
       <c r="P5" t="n">
-        <v>155146</v>
+        <v>66871</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999843239784241</v>
+        <v>0.9999991655349731</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9517386555671692</v>
+        <v>0.9119889140129089</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9353173971176147</v>
+        <v>0.8834359645843506</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9749102592468262</v>
+        <v>0.9562335610389709</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9947665929794312</v>
+        <v>0.9910489320755005</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9891360998153687</v>
+        <v>0.9795231819152832</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9969034790992737</v>
+        <v>0.9939514398574829</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>40062</v>
+        <v>8050</v>
       </c>
       <c r="Z5" t="n">
-        <v>425133</v>
+        <v>85383</v>
       </c>
       <c r="AA5" t="n">
-        <v>3997548</v>
+        <v>800192</v>
       </c>
       <c r="AB5" t="n">
-        <v>49729</v>
+        <v>9974</v>
       </c>
       <c r="AC5" t="n">
-        <v>145659</v>
+        <v>29187</v>
       </c>
       <c r="AD5" t="n">
-        <v>3165</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1066983</v>
+        <v>213804</v>
       </c>
       <c r="AG5" t="n">
-        <v>1468497</v>
+        <v>294510</v>
       </c>
       <c r="AH5" t="n">
-        <v>663748</v>
+        <v>133227</v>
       </c>
       <c r="AI5" t="n">
-        <v>150705</v>
+        <v>30232</v>
       </c>
       <c r="AJ5" t="n">
-        <v>250399</v>
+        <v>50139</v>
       </c>
       <c r="AK5" t="n">
-        <v>66400</v>
+        <v>13301</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.973541259765625</v>
+        <v>0.9734675884246826</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.964300811290741</v>
+        <v>0.9642073512077332</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.983773410320282</v>
+        <v>0.9837334752082825</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963125586509705</v>
+        <v>0.9963013529777527</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938787817955017</v>
+        <v>0.9938697814941406</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983751177787781</v>
+        <v>0.998373806476593</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>41862</v>
+        <v>13514</v>
       </c>
       <c r="E6" t="n">
-        <v>75953</v>
+        <v>19922</v>
       </c>
       <c r="F6" t="n">
-        <v>91942</v>
+        <v>27114</v>
       </c>
       <c r="G6" t="n">
-        <v>191787</v>
+        <v>16742</v>
       </c>
       <c r="H6" t="n">
-        <v>41059</v>
+        <v>11000</v>
       </c>
       <c r="I6" t="n">
-        <v>2969</v>
+        <v>961</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>32262</v>
+        <v>6482</v>
       </c>
       <c r="Z6" t="n">
-        <v>26748</v>
+        <v>5366</v>
       </c>
       <c r="AA6" t="n">
-        <v>54395</v>
+        <v>10913</v>
       </c>
       <c r="AB6" t="n">
-        <v>294942</v>
+        <v>59026</v>
       </c>
       <c r="AC6" t="n">
-        <v>34895</v>
+        <v>6990</v>
       </c>
       <c r="AD6" t="n">
-        <v>2405</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>419</v>
+        <v>316</v>
       </c>
       <c r="E7" t="n">
-        <v>40416</v>
+        <v>21998</v>
       </c>
       <c r="F7" t="n">
-        <v>258008</v>
+        <v>95535</v>
       </c>
       <c r="G7" t="n">
-        <v>84481</v>
+        <v>37805</v>
       </c>
       <c r="H7" t="n">
-        <v>2083148</v>
+        <v>330086</v>
       </c>
       <c r="I7" t="n">
-        <v>79374</v>
+        <v>23812</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>139</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>4050</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>148103</v>
+        <v>29666</v>
       </c>
       <c r="AB7" t="n">
-        <v>37897</v>
+        <v>7593</v>
       </c>
       <c r="AC7" t="n">
-        <v>2295467</v>
+        <v>459413</v>
       </c>
       <c r="AD7" t="n">
-        <v>60210</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>73</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>104</v>
+        <v>45</v>
       </c>
       <c r="E8" t="n">
-        <v>1957</v>
+        <v>1069</v>
       </c>
       <c r="F8" t="n">
-        <v>8573</v>
+        <v>4336</v>
       </c>
       <c r="G8" t="n">
-        <v>3961</v>
+        <v>2041</v>
       </c>
       <c r="H8" t="n">
-        <v>140478</v>
+        <v>59374</v>
       </c>
       <c r="I8" t="n">
-        <v>811439</v>
+        <v>126522</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>140</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>405</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1651</v>
+        <v>331</v>
       </c>
       <c r="AB8" t="n">
-        <v>1327</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>62877</v>
+        <v>12595</v>
       </c>
       <c r="AD8" t="n">
-        <v>900185</v>
+        <v>180092</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
